--- a/R Markdown/resultados/tabela_teste_estatistico_2025.xlsx
+++ b/R Markdown/resultados/tabela_teste_estatistico_2025.xlsx
@@ -403,22 +403,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9999999999999996</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="C2">
-        <v>1.951563910473908E-18</v>
+        <v>-9.75781955236954E-19</v>
       </c>
       <c r="D2">
-        <v>-0.008623903122190227</v>
+        <v>-0.008660384060333388</v>
       </c>
       <c r="E2">
-        <v>0.008623903122190231</v>
+        <v>0.008660384060333384</v>
       </c>
       <c r="F2">
-        <v>0.1393611006145131</v>
+        <v>0.1395724067355961</v>
       </c>
       <c r="G2">
-        <v>0.5183784530413742</v>
+        <v>0.5164588638745815</v>
       </c>
       <c r="H2">
         <v>32</v>
